--- a/data/trans_orig/IP07A14-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07A14-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse feliz en casa en 2007 (tasa de respuesta: 99,5%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa, percibida por el adulto en 2007 (tasa de respuesta: 99,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5341</t>
+          <t>5396</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12716</t>
+          <t>12569</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10551</t>
+          <t>10354</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20280</t>
+          <t>19653</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17981</t>
+          <t>17983</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29128</t>
+          <t>30060</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>56,62%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5884</t>
+          <t>5733</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13088</t>
+          <t>13217</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7876</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16483</t>
+          <t>16655</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15889</t>
+          <t>16064</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27776</t>
+          <t>27671</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>52,12%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1781</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7714</t>
+          <t>7846</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6945</t>
+          <t>7159</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t>4388</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12640</t>
+          <t>12136</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>22,86%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23998</t>
+          <t>24533</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33968</t>
+          <t>34102</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38344</t>
+          <t>38019</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48319</t>
+          <t>48485</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65479</t>
+          <t>65621</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80369</t>
+          <t>80293</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,13%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9061</t>
+          <t>9214</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18934</t>
+          <t>18677</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7994</t>
+          <t>7969</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17820</t>
+          <t>18328</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18826</t>
+          <t>19204</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>34033</t>
+          <t>33730</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,24%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3172</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3860</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4453</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3321</t>
+          <t>3606</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16952</t>
+          <t>16946</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26563</t>
+          <t>26348</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17130</t>
+          <t>17005</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24680</t>
+          <t>25177</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37224</t>
+          <t>37179</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48830</t>
+          <t>50351</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>76,96%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8574</t>
+          <t>8789</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18185</t>
+          <t>18191</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4905</t>
+          <t>4994</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12077</t>
+          <t>12525</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15957</t>
+          <t>14957</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27286</t>
+          <t>27507</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>42,04%</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3572</t>
+          <t>3590</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15720</t>
+          <t>16660</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26388</t>
+          <t>26800</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17269</t>
+          <t>16711</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27118</t>
+          <t>26830</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36000</t>
+          <t>35865</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50655</t>
+          <t>50644</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,18%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12149</t>
+          <t>11756</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22748</t>
+          <t>21790</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>9711</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>18988</t>
+          <t>19700</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>24493</t>
+          <t>24917</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>38781</t>
+          <t>39041</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>50,25%</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3976</t>
+          <t>4799</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>591</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5076</t>
+          <t>5587</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>804</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7086</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10970</t>
+          <t>11104</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17205</t>
+          <t>17228</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>9890</t>
+          <t>10468</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17664</t>
+          <t>17640</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>23042</t>
+          <t>23581</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>33328</t>
+          <t>33329</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,63%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7520</t>
+          <t>7466</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4257</t>
+          <t>4213</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12007</t>
+          <t>11853</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7264</t>
+          <t>7338</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>16734</t>
+          <t>17305</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>40,82%</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4280</t>
+          <t>4268</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>3457</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,13%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14039</t>
+          <t>14130</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>22121</t>
+          <t>22122</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>14203</t>
+          <t>13627</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>21948</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>30049</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>42021</t>
+          <t>42049</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>72,37%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5377</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>12850</t>
+          <t>13134</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>6065</t>
+          <t>6234</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>13743</t>
+          <t>14198</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>13446</t>
+          <t>13523</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>24971</t>
+          <t>24835</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,74%</t>
         </is>
       </c>
     </row>
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>620</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>5470</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>616</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5640</t>
+          <t>5629</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3466</t>
+          <t>3487</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3468</t>
+          <t>4184</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>29182</t>
+          <t>30114</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>41279</t>
+          <t>41393</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>32230</t>
+          <t>31821</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>44252</t>
+          <t>44731</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>64778</t>
+          <t>64830</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>81796</t>
+          <t>82578</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>69,34%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>13875</t>
+          <t>14038</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>26133</t>
+          <t>25533</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>16936</t>
+          <t>16959</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>29070</t>
+          <t>29146</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>34643</t>
+          <t>33897</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>51064</t>
+          <t>51714</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>43,43%</t>
         </is>
       </c>
     </row>
@@ -5055,7 +5055,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>4283</t>
+          <t>4342</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>4710</t>
+          <t>4150</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>693</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>6270</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>31037</t>
+          <t>31262</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>44621</t>
+          <t>45565</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>34649</t>
+          <t>35031</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>48163</t>
+          <t>47773</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>70301</t>
+          <t>69437</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>89049</t>
+          <t>88929</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>59,87%</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>27291</t>
+          <t>26552</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>40723</t>
+          <t>40786</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>24445</t>
+          <t>24817</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>38565</t>
+          <t>37814</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>55864</t>
+          <t>55497</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>75214</t>
+          <t>74870</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,41%</t>
         </is>
       </c>
     </row>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>654</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>6273</t>
+          <t>6603</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>4190</t>
+          <t>4343</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1464</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>8221</t>
+          <t>8003</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>173881</t>
+          <t>174321</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>202363</t>
+          <t>202776</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>200880</t>
+          <t>200621</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>229271</t>
+          <t>229733</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>382105</t>
+          <t>383336</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>422273</t>
+          <t>424445</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>63,75%</t>
         </is>
       </c>
     </row>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>104517</t>
+          <t>105433</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>133432</t>
+          <t>133922</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>104025</t>
+          <t>103871</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>131365</t>
+          <t>132051</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>217383</t>
+          <t>216791</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>257534</t>
+          <t>258134</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,77%</t>
         </is>
       </c>
     </row>
@@ -6414,12 +6414,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>6654</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>18643</t>
+          <t>18268</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>7646</t>
+          <t>8009</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>19634</t>
+          <t>19234</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6484,12 +6484,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>17706</t>
+          <t>17449</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>32249</t>
+          <t>32646</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>3195</t>
+          <t>4154</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6602,7 +6602,7 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6911,7 +6911,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse feliz en casa en 2012 (tasa de respuesta: 97,81%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa, percibida por el adulto en 2012 (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7106,12 +7106,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12969</t>
+          <t>13288</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20019</t>
+          <t>20169</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17036</t>
+          <t>17062</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24868</t>
+          <t>25209</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32302</t>
+          <t>31445</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43124</t>
+          <t>43203</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,86%</t>
         </is>
       </c>
     </row>
@@ -7219,12 +7219,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2721</t>
+          <t>2659</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9585</t>
+          <t>9242</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7254,12 +7254,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>3638</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10990</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7289,12 +7289,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8378</t>
+          <t>7895</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17832</t>
+          <t>17889</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,07%</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>4081</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5697</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>840</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7042</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -7788,12 +7788,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30322</t>
+          <t>30186</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40283</t>
+          <t>39810</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41531</t>
+          <t>40879</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49831</t>
+          <t>49358</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>75413</t>
+          <t>74643</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>87351</t>
+          <t>87645</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7873,12 +7873,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,91%</t>
         </is>
       </c>
     </row>
@@ -7901,12 +7901,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5984</t>
+          <t>6556</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15396</t>
+          <t>15780</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10804</t>
+          <t>11393</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7951,12 +7951,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11619</t>
+          <t>11106</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23492</t>
+          <t>23190</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,0%</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5424</t>
+          <t>4268</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3983</t>
+          <t>3674</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5521</t>
+          <t>5760</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3410</t>
+          <t>3453</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3404</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8470,12 +8470,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17555</t>
+          <t>17621</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24058</t>
+          <t>24079</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8485,12 +8485,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16671</t>
+          <t>16439</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25249</t>
+          <t>25375</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36886</t>
+          <t>36664</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47319</t>
+          <t>47465</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,85%</t>
         </is>
       </c>
     </row>
@@ -8583,12 +8583,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7966</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8598,12 +8598,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8618,12 +8618,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>5744</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14090</t>
+          <t>14334</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9454</t>
+          <t>9036</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19752</t>
+          <t>19631</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,26%</t>
         </is>
       </c>
     </row>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3700</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3453</t>
+          <t>3462</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -9152,12 +9152,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14067</t>
+          <t>13357</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24145</t>
+          <t>23750</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14075</t>
+          <t>13830</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24219</t>
+          <t>23977</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30481</t>
+          <t>31060</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44603</t>
+          <t>44870</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>61,49%</t>
         </is>
       </c>
     </row>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14042</t>
+          <t>14437</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24120</t>
+          <t>24830</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9280,12 +9280,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9300,12 +9300,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8647</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>18113</t>
+          <t>18334</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9335,12 +9335,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>25955</t>
+          <t>25542</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>40148</t>
+          <t>40084</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>54,93%</t>
         </is>
       </c>
     </row>
@@ -9413,12 +9413,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>758</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5533</t>
+          <t>5997</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>651</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6203</t>
+          <t>6538</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -9834,12 +9834,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>13158</t>
+          <t>13111</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>19217</t>
+          <t>19212</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13783</t>
+          <t>13632</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19511</t>
+          <t>19513</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>29154</t>
+          <t>29237</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>37903</t>
+          <t>37393</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>90,29%</t>
         </is>
       </c>
     </row>
@@ -9947,12 +9947,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7451</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9982,12 +9982,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>7172</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3510</t>
+          <t>4020</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>12259</t>
+          <t>12176</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,4%</t>
         </is>
       </c>
     </row>
@@ -10516,12 +10516,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>15623</t>
+          <t>16168</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>24146</t>
+          <t>24207</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>11753</t>
+          <t>11543</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>20047</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>30193</t>
+          <t>30522</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>42460</t>
+          <t>42588</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>76,06%</t>
         </is>
       </c>
     </row>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5595</t>
+          <t>5534</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>14118</t>
+          <t>13573</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10644,12 +10644,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10664,12 +10664,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>6150</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>14503</t>
+          <t>14713</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10699,12 +10699,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>13536</t>
+          <t>13408</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>25803</t>
+          <t>25474</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>45,49%</t>
         </is>
       </c>
     </row>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>29780</t>
+          <t>29480</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>42299</t>
+          <t>41607</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11213,12 +11213,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11233,12 +11233,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>31694</t>
+          <t>32359</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>43631</t>
+          <t>43586</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11268,12 +11268,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>65528</t>
+          <t>64538</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>81972</t>
+          <t>81206</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>72,51%</t>
         </is>
       </c>
     </row>
@@ -11311,12 +11311,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>13757</t>
+          <t>14522</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>26387</t>
+          <t>26514</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11326,12 +11326,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>11002</t>
+          <t>11100</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>23029</t>
+          <t>22463</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11381,12 +11381,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>28506</t>
+          <t>29163</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>45004</t>
+          <t>45568</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11396,12 +11396,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,69%</t>
         </is>
       </c>
     </row>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>3349</t>
+          <t>3828</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3193</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4678</t>
+          <t>4584</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -11880,12 +11880,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>23891</t>
+          <t>24076</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>37812</t>
+          <t>38763</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11895,12 +11895,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11915,12 +11915,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>30182</t>
+          <t>30964</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>44940</t>
+          <t>44849</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11930,12 +11930,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>58062</t>
+          <t>57846</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>79479</t>
+          <t>78887</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11965,12 +11965,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,02%</t>
         </is>
       </c>
     </row>
@@ -11993,12 +11993,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>36437</t>
+          <t>36190</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>51037</t>
+          <t>51099</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12028,12 +12028,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>25404</t>
+          <t>26148</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>40260</t>
+          <t>40315</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12043,12 +12043,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>67290</t>
+          <t>66433</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>88594</t>
+          <t>87434</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12078,12 +12078,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>55,44%</t>
         </is>
       </c>
     </row>
@@ -12106,12 +12106,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>8957</t>
+          <t>9204</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3801</t>
+          <t>4027</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>12233</t>
+          <t>12220</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>7194</t>
+          <t>7374</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>18027</t>
+          <t>18380</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -12259,7 +12259,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12294,7 +12294,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>3099</t>
+          <t>3451</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12309,7 +12309,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -12562,12 +12562,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>182340</t>
+          <t>180646</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>210974</t>
+          <t>210346</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>204120</t>
+          <t>203541</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>231921</t>
+          <t>229957</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12612,12 +12612,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>392738</t>
+          <t>394004</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>432944</t>
+          <t>434928</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12647,12 +12647,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,67%</t>
         </is>
       </c>
     </row>
@@ -12675,12 +12675,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>102400</t>
+          <t>102923</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>130750</t>
+          <t>131685</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>85080</t>
+          <t>88574</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>112838</t>
+          <t>113729</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12725,12 +12725,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>197831</t>
+          <t>195150</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>237598</t>
+          <t>236079</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,19%</t>
         </is>
       </c>
     </row>
@@ -12788,12 +12788,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>3709</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>13115</t>
+          <t>12874</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12823,12 +12823,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>8006</t>
+          <t>7877</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>19400</t>
+          <t>19324</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12838,12 +12838,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>13394</t>
+          <t>13973</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>28033</t>
+          <t>29077</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12956,7 +12956,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12976,7 +12976,7 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>4643</t>
+          <t>4169</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -13019,7 +13019,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>4398</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13089,7 +13089,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>3374</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13285,7 +13285,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse feliz en casa en 2016 (tasa de respuesta: 98,72%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa, percibida por el adulto en 2016 (tasa de respuesta: 98,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16405</t>
+          <t>16610</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24801</t>
+          <t>24526</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13495,12 +13495,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13515,12 +13515,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15888</t>
+          <t>15728</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24142</t>
+          <t>24187</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13530,12 +13530,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13550,12 +13550,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35238</t>
+          <t>35603</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46970</t>
+          <t>47024</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13565,12 +13565,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,31%</t>
         </is>
       </c>
     </row>
@@ -13593,12 +13593,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10555</t>
+          <t>11139</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13608,12 +13608,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13628,12 +13628,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3580</t>
+          <t>3473</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11806</t>
+          <t>11545</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13663,12 +13663,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8625</t>
+          <t>8472</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19415</t>
+          <t>19421</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,58%</t>
         </is>
       </c>
     </row>
@@ -13706,12 +13706,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>5523</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13721,12 +13721,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13746,7 +13746,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13761,7 +13761,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>684</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7738</t>
+          <t>6801</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>11,76%</t>
         </is>
       </c>
     </row>
@@ -14162,12 +14162,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40411</t>
+          <t>40629</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48903</t>
+          <t>48961</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14177,12 +14177,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14197,12 +14197,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47885</t>
+          <t>47654</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55077</t>
+          <t>55111</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14212,12 +14212,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14232,12 +14232,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91861</t>
+          <t>91143</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>102899</t>
+          <t>102342</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14247,12 +14247,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>92,96%</t>
         </is>
       </c>
     </row>
@@ -14275,12 +14275,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4014</t>
+          <t>3956</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12506</t>
+          <t>12288</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14290,12 +14290,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14310,12 +14310,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9290</t>
+          <t>9521</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14325,12 +14325,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14345,12 +14345,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7193</t>
+          <t>7750</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18231</t>
+          <t>18949</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14360,12 +14360,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>17,21%</t>
         </is>
       </c>
     </row>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18606</t>
+          <t>18294</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29233</t>
+          <t>28416</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -14859,12 +14859,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14879,12 +14879,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19374</t>
+          <t>19197</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28085</t>
+          <t>27704</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14894,12 +14894,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14914,12 +14914,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39984</t>
+          <t>40914</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54372</t>
+          <t>54067</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14929,12 +14929,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>77,72%</t>
         </is>
       </c>
     </row>
@@ -14957,12 +14957,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6603</t>
+          <t>7420</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17230</t>
+          <t>17542</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -14972,12 +14972,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14992,12 +14992,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5643</t>
+          <t>6024</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14354</t>
+          <t>14531</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15007,12 +15007,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15027,12 +15027,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15192</t>
+          <t>15497</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29580</t>
+          <t>28650</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15042,12 +15042,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>41,19%</t>
         </is>
       </c>
     </row>
@@ -15526,12 +15526,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28717</t>
+          <t>28116</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>36508</t>
+          <t>36484</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15541,12 +15541,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15561,12 +15561,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32718</t>
+          <t>32777</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40454</t>
+          <t>40413</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15576,12 +15576,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15596,12 +15596,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>64514</t>
+          <t>63940</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>75389</t>
+          <t>75444</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15611,12 +15611,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,64%</t>
         </is>
       </c>
     </row>
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10782</t>
+          <t>11184</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15654,12 +15654,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15674,12 +15674,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8693</t>
+          <t>8878</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15689,12 +15689,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -15709,12 +15709,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6159</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>16284</t>
+          <t>16672</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15724,12 +15724,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>20,03%</t>
         </is>
       </c>
     </row>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2598</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15772,7 +15772,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>4403</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15822,12 +15822,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>620</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>6092</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15842,7 +15842,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -16208,12 +16208,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10150</t>
+          <t>9623</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16223,12 +16223,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16243,12 +16243,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>3435</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11394</t>
+          <t>11182</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16258,12 +16258,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16278,12 +16278,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>8687</t>
+          <t>8330</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>18528</t>
+          <t>18263</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16293,12 +16293,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,26%</t>
         </is>
       </c>
     </row>
@@ -16321,12 +16321,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>8527</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15653</t>
+          <t>15614</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16336,12 +16336,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11412</t>
+          <t>11219</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>19555</t>
+          <t>19685</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16371,12 +16371,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16391,12 +16391,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>22455</t>
+          <t>21926</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>33033</t>
+          <t>32568</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16406,12 +16406,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>71,79%</t>
         </is>
       </c>
     </row>
@@ -16439,7 +16439,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>5485</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16469,12 +16469,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>641</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6499</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16484,12 +16484,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9473</t>
+          <t>9334</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16519,12 +16519,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,57%</t>
         </is>
       </c>
     </row>
@@ -16890,12 +16890,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>19611</t>
+          <t>19970</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>27320</t>
+          <t>27272</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16905,12 +16905,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16925,12 +16925,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>22482</t>
+          <t>22443</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>29011</t>
+          <t>29035</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16940,12 +16940,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>44451</t>
+          <t>45209</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>55177</t>
+          <t>55044</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16975,12 +16975,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,64%</t>
         </is>
       </c>
     </row>
@@ -17003,12 +17003,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2759</t>
+          <t>2840</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>10048</t>
+          <t>10013</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17018,12 +17018,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -17038,12 +17038,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>836</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>7242</t>
+          <t>7123</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17053,12 +17053,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>5015</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>14908</t>
+          <t>14209</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17088,12 +17088,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>23,14%</t>
         </is>
       </c>
     </row>
@@ -17156,7 +17156,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17191,7 +17191,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17206,7 +17206,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -17347,7 +17347,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17362,7 +17362,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17417,7 +17417,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>4225</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17432,7 +17432,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -17572,12 +17572,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>25832</t>
+          <t>25659</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>39696</t>
+          <t>39236</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -17587,12 +17587,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -17607,12 +17607,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>24892</t>
+          <t>24855</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>37960</t>
+          <t>38398</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -17622,12 +17622,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>54325</t>
+          <t>54303</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>73534</t>
+          <t>73245</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -17657,12 +17657,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>55,7%</t>
         </is>
       </c>
     </row>
@@ -17685,12 +17685,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>23937</t>
+          <t>24764</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>37575</t>
+          <t>37977</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -17700,12 +17700,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -17720,12 +17720,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>23828</t>
+          <t>23575</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>36892</t>
+          <t>37191</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -17735,12 +17735,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -17755,12 +17755,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>51950</t>
+          <t>52440</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>71252</t>
+          <t>71426</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -17770,12 +17770,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>54,32%</t>
         </is>
       </c>
     </row>
@@ -17798,12 +17798,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>8703</t>
+          <t>8187</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -17813,12 +17813,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -17833,12 +17833,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>700</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>5930</t>
+          <t>5850</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -17853,7 +17853,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -17868,12 +17868,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>2752</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>10922</t>
+          <t>10739</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -17883,12 +17883,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -18254,12 +18254,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>33508</t>
+          <t>33611</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>47972</t>
+          <t>47573</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -18269,12 +18269,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -18289,12 +18289,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>34420</t>
+          <t>33824</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>49662</t>
+          <t>48599</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -18304,12 +18304,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>63,58%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -18324,12 +18324,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>72173</t>
+          <t>72038</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>92373</t>
+          <t>91510</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -18339,12 +18339,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>58,31%</t>
         </is>
       </c>
     </row>
@@ -18367,12 +18367,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>26570</t>
+          <t>25995</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>41283</t>
+          <t>40539</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -18382,12 +18382,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -18402,12 +18402,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>24602</t>
+          <t>25475</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>39027</t>
+          <t>40282</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -18417,12 +18417,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -18437,12 +18437,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>55777</t>
+          <t>56589</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>75965</t>
+          <t>76268</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -18452,12 +18452,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,6%</t>
         </is>
       </c>
     </row>
@@ -18480,12 +18480,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3122</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>10939</t>
+          <t>11153</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -18495,12 +18495,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -18520,7 +18520,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>6613</t>
+          <t>5972</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -18535,7 +18535,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -18550,12 +18550,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>4831</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>13669</t>
+          <t>14464</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -18565,12 +18565,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -18936,12 +18936,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>212762</t>
+          <t>212785</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>242260</t>
+          <t>241958</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -18956,7 +18956,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -18971,12 +18971,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>225622</t>
+          <t>226462</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>253489</t>
+          <t>254945</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -18986,12 +18986,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -19006,12 +19006,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>445240</t>
+          <t>443888</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>488932</t>
+          <t>485465</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -19021,12 +19021,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>67,81%</t>
         </is>
       </c>
     </row>
@@ -19049,12 +19049,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>101117</t>
+          <t>99988</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>130493</t>
+          <t>128408</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -19064,12 +19064,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>95367</t>
+          <t>94434</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>122534</t>
+          <t>121460</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -19099,12 +19099,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -19119,12 +19119,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>201472</t>
+          <t>204383</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>242365</t>
+          <t>243942</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -19162,12 +19162,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>8857</t>
+          <t>9293</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>20773</t>
+          <t>21931</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -19177,82 +19177,82 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>6,15%</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>10760</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>6362</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>16910</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>4,71%</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>25157</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>17768</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>34209</t>
+        </is>
+      </c>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>3,51%</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
           <t>2,48%</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>5,82%</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>10760</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>6278</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>16957</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
-      <c r="O54" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="P54" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
-      <c r="Q54" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="R54" s="2" t="inlineStr">
-        <is>
-          <t>25157</t>
-        </is>
-      </c>
-      <c r="S54" s="2" t="inlineStr">
-        <is>
-          <t>18560</t>
-        </is>
-      </c>
-      <c r="T54" s="2" t="inlineStr">
-        <is>
-          <t>35355</t>
-        </is>
-      </c>
-      <c r="U54" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="V54" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -19393,7 +19393,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -19408,7 +19408,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -19463,7 +19463,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>6242</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -19478,7 +19478,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
